--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:02</t>
+    <t xml:space="preserve">2026-09-10 01:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:14</t>
+    <t xml:space="preserve">2026-09-12 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_coquimbo.xlsx
@@ -66,6 +66,9 @@
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:26</t>
+    <t xml:space="preserve">2026-09-23 23:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,13 +704,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28.55</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="14">
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4302</v>
+        <v>4106</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>26.81</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4305</v>
+        <v>4302</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>25.44</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4305</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>25.44</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>
